--- a/dados_excel/round_state_winrates.xlsx
+++ b/dados_excel/round_state_winrates.xlsx
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1930</v>
+        <v>3334</v>
       </c>
       <c r="C2" t="n">
-        <v>965</v>
+        <v>1667</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.5</v>
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2401</v>
+        <v>4226</v>
       </c>
       <c r="C3" t="n">
-        <v>386</v>
+        <v>629</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.1607663473552687</v>
+        <v>0.148840511121628</v>
       </c>
     </row>
     <row r="4">
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2611</v>
+        <v>4459</v>
       </c>
       <c r="C4" t="n">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.04404442742244351</v>
+        <v>0.03767660910518053</v>
       </c>
     </row>
     <row r="5">
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2067</v>
+        <v>3688</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.00822447992259313</v>
+        <v>0.007863340563991324</v>
       </c>
     </row>
     <row r="6">
@@ -526,13 +526,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>947</v>
+        <v>1776</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.002111932418162619</v>
+        <v>0.002252252252252252</v>
       </c>
     </row>
     <row r="7">
@@ -542,13 +542,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2401</v>
+        <v>4226</v>
       </c>
       <c r="C7" t="n">
-        <v>2015</v>
+        <v>3597</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.8392336526447314</v>
+        <v>0.851159488878372</v>
       </c>
     </row>
     <row r="8">
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2900</v>
+        <v>5162</v>
       </c>
       <c r="C8" t="n">
-        <v>1450</v>
+        <v>2581</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.5</v>
@@ -574,13 +574,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3291</v>
+        <v>5711</v>
       </c>
       <c r="C9" t="n">
-        <v>710</v>
+        <v>1235</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.2157398966879368</v>
+        <v>0.2162493433724391</v>
       </c>
     </row>
     <row r="10">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3050</v>
+        <v>5325</v>
       </c>
       <c r="C10" t="n">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.09081967213114754</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="11">
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1689</v>
+        <v>3063</v>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.02960331557134399</v>
+        <v>0.02448579823702253</v>
       </c>
     </row>
     <row r="12">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2611</v>
+        <v>4459</v>
       </c>
       <c r="C12" t="n">
-        <v>2496</v>
+        <v>4291</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.9559555725775565</v>
+        <v>0.9623233908948194</v>
       </c>
     </row>
     <row r="13">
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3291</v>
+        <v>5711</v>
       </c>
       <c r="C13" t="n">
-        <v>2581</v>
+        <v>4476</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.7842601033120632</v>
+        <v>0.7837506566275608</v>
       </c>
     </row>
     <row r="14">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3928</v>
+        <v>6894</v>
       </c>
       <c r="C14" t="n">
-        <v>1964</v>
+        <v>3447</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0.5</v>
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4300</v>
+        <v>7525</v>
       </c>
       <c r="C15" t="n">
-        <v>1086</v>
+        <v>1924</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.2525581395348837</v>
+        <v>0.2556810631229236</v>
       </c>
     </row>
     <row r="16">
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3096</v>
+        <v>5552</v>
       </c>
       <c r="C16" t="n">
-        <v>359</v>
+        <v>611</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.1159560723514212</v>
+        <v>0.1100504322766571</v>
       </c>
     </row>
     <row r="17">
@@ -702,13 +702,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2067</v>
+        <v>3688</v>
       </c>
       <c r="C17" t="n">
-        <v>2050</v>
+        <v>3659</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.9917755200774069</v>
+        <v>0.9921366594360087</v>
       </c>
     </row>
     <row r="18">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3050</v>
+        <v>5325</v>
       </c>
       <c r="C18" t="n">
-        <v>2773</v>
+        <v>4899</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.9091803278688525</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="19">
@@ -734,13 +734,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4300</v>
+        <v>7525</v>
       </c>
       <c r="C19" t="n">
-        <v>3214</v>
+        <v>5601</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.7474418604651163</v>
+        <v>0.7443189368770764</v>
       </c>
     </row>
     <row r="20">
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5822</v>
+        <v>10128</v>
       </c>
       <c r="C20" t="n">
-        <v>2911</v>
+        <v>5064</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0.5</v>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5983</v>
+        <v>10594</v>
       </c>
       <c r="C21" t="n">
-        <v>1652</v>
+        <v>3069</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.2761156610396122</v>
+        <v>0.2896922786482915</v>
       </c>
     </row>
     <row r="22">
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>947</v>
+        <v>1776</v>
       </c>
       <c r="C22" t="n">
-        <v>945</v>
+        <v>1772</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.9978880675818373</v>
+        <v>0.9977477477477478</v>
       </c>
     </row>
     <row r="23">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1689</v>
+        <v>3063</v>
       </c>
       <c r="C23" t="n">
-        <v>1639</v>
+        <v>2988</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.970396684428656</v>
+        <v>0.9755142017629774</v>
       </c>
     </row>
     <row r="24">
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3096</v>
+        <v>5552</v>
       </c>
       <c r="C24" t="n">
-        <v>2737</v>
+        <v>4941</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.8840439276485789</v>
+        <v>0.889949567723343</v>
       </c>
     </row>
     <row r="25">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5983</v>
+        <v>10594</v>
       </c>
       <c r="C25" t="n">
-        <v>4331</v>
+        <v>7525</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.7238843389603877</v>
+        <v>0.7103077213517085</v>
       </c>
     </row>
     <row r="26">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11862</v>
+        <v>21018</v>
       </c>
       <c r="C26" t="n">
-        <v>5931</v>
+        <v>10509</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0.5</v>

--- a/dados_excel/round_state_winrates.xlsx
+++ b/dados_excel/round_state_winrates.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="round_state_winrates" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="round_state_winrates" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'round_state_winrates'!$A$1:$D$26</definedName>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3334</v>
+        <v>4036</v>
       </c>
       <c r="C2" t="n">
-        <v>1667</v>
+        <v>2018</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.5</v>
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4226</v>
+        <v>5067</v>
       </c>
       <c r="C3" t="n">
-        <v>629</v>
+        <v>782</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.148840511121628</v>
+        <v>0.1543319518452733</v>
       </c>
     </row>
     <row r="4">
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4459</v>
+        <v>5286</v>
       </c>
       <c r="C4" t="n">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.03767660910518053</v>
+        <v>0.03934922436625047</v>
       </c>
     </row>
     <row r="5">
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3688</v>
+        <v>4364</v>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.007863340563991324</v>
+        <v>0.008707607699358386</v>
       </c>
     </row>
     <row r="6">
@@ -526,13 +526,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1776</v>
+        <v>2094</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.002252252252252252</v>
+        <v>0.001910219675262655</v>
       </c>
     </row>
     <row r="7">
@@ -542,13 +542,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4226</v>
+        <v>5067</v>
       </c>
       <c r="C7" t="n">
-        <v>3597</v>
+        <v>4285</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.851159488878372</v>
+        <v>0.8456680481547266</v>
       </c>
     </row>
     <row r="8">
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5162</v>
+        <v>6210</v>
       </c>
       <c r="C8" t="n">
-        <v>2581</v>
+        <v>3105</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.5</v>
@@ -574,13 +574,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5711</v>
+        <v>6811</v>
       </c>
       <c r="C9" t="n">
-        <v>1235</v>
+        <v>1484</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.2162493433724391</v>
+        <v>0.2178828365878726</v>
       </c>
     </row>
     <row r="10">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5325</v>
+        <v>6267</v>
       </c>
       <c r="C10" t="n">
-        <v>426</v>
+        <v>502</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.08</v>
+        <v>0.08010212222754109</v>
       </c>
     </row>
     <row r="11">
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3063</v>
+        <v>3607</v>
       </c>
       <c r="C11" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.02448579823702253</v>
+        <v>0.02328805101192126</v>
       </c>
     </row>
     <row r="12">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4459</v>
+        <v>5286</v>
       </c>
       <c r="C12" t="n">
-        <v>4291</v>
+        <v>5078</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.9623233908948194</v>
+        <v>0.9606507756337496</v>
       </c>
     </row>
     <row r="13">
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5711</v>
+        <v>6811</v>
       </c>
       <c r="C13" t="n">
-        <v>4476</v>
+        <v>5327</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.7837506566275608</v>
+        <v>0.7821171634121274</v>
       </c>
     </row>
     <row r="14">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6894</v>
+        <v>8314</v>
       </c>
       <c r="C14" t="n">
-        <v>3447</v>
+        <v>4157</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0.5</v>
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7525</v>
+        <v>8956</v>
       </c>
       <c r="C15" t="n">
-        <v>1924</v>
+        <v>2327</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.2556810631229236</v>
+        <v>0.259825815096025</v>
       </c>
     </row>
     <row r="16">
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5552</v>
+        <v>6565</v>
       </c>
       <c r="C16" t="n">
-        <v>611</v>
+        <v>724</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.1100504322766571</v>
+        <v>0.1102817974105103</v>
       </c>
     </row>
     <row r="17">
@@ -702,13 +702,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3688</v>
+        <v>4364</v>
       </c>
       <c r="C17" t="n">
-        <v>3659</v>
+        <v>4326</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.9921366594360087</v>
+        <v>0.9912923923006416</v>
       </c>
     </row>
     <row r="18">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5325</v>
+        <v>6267</v>
       </c>
       <c r="C18" t="n">
-        <v>4899</v>
+        <v>5765</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.92</v>
+        <v>0.9198978777724589</v>
       </c>
     </row>
     <row r="19">
@@ -734,13 +734,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7525</v>
+        <v>8956</v>
       </c>
       <c r="C19" t="n">
-        <v>5601</v>
+        <v>6629</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.7443189368770764</v>
+        <v>0.740174184903975</v>
       </c>
     </row>
     <row r="20">
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10128</v>
+        <v>12058</v>
       </c>
       <c r="C20" t="n">
-        <v>5064</v>
+        <v>6029</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0.5</v>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10594</v>
+        <v>12572</v>
       </c>
       <c r="C21" t="n">
-        <v>3069</v>
+        <v>3632</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.2896922786482915</v>
+        <v>0.2888959592745785</v>
       </c>
     </row>
     <row r="22">
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1776</v>
+        <v>2094</v>
       </c>
       <c r="C22" t="n">
-        <v>1772</v>
+        <v>2090</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.9977477477477478</v>
+        <v>0.9980897803247374</v>
       </c>
     </row>
     <row r="23">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3063</v>
+        <v>3607</v>
       </c>
       <c r="C23" t="n">
-        <v>2988</v>
+        <v>3523</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.9755142017629774</v>
+        <v>0.9767119489880788</v>
       </c>
     </row>
     <row r="24">
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5552</v>
+        <v>6565</v>
       </c>
       <c r="C24" t="n">
-        <v>4941</v>
+        <v>5841</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.889949567723343</v>
+        <v>0.8897182025894897</v>
       </c>
     </row>
     <row r="25">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10594</v>
+        <v>12572</v>
       </c>
       <c r="C25" t="n">
-        <v>7525</v>
+        <v>8940</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.7103077213517085</v>
+        <v>0.7111040407254215</v>
       </c>
     </row>
     <row r="26">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>21018</v>
+        <v>24974</v>
       </c>
       <c r="C26" t="n">
-        <v>10509</v>
+        <v>12487</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0.5</v>
